--- a/artfynd/S 2365-2025 artfynd.xlsx
+++ b/artfynd/S 2365-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,32 +1032,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134910787</v>
+        <v>77690699</v>
       </c>
       <c r="B5" t="n">
-        <v>45050</v>
+        <v>58129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102018</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,28 +1065,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>925 m OSO Petersborg, Sm</t>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553958</v>
+        <v>553976</v>
       </c>
       <c r="R5" t="n">
-        <v>6286375</v>
+        <v>6287332</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,17 +1113,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På Hieracium canistrale-korg</t>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,39 +1137,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Vägslänt mot dike</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Eric Lundén</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Nilsson</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Nilsson</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>77690699</v>
+        <v>79153696</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>58039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,37 +1166,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1239,22 +1236,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I hagen väster om vägen i ett slånsnår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79153696</v>
+        <v>95783582</v>
       </c>
       <c r="B7" t="n">
-        <v>58039</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,50 +1294,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+          <t>Göstorp,Nybro, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553976</v>
+        <v>553374</v>
       </c>
       <c r="R7" t="n">
-        <v>6287332</v>
+        <v>6286783</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,27 +1356,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I hagen väster om vägen i ett slånsnår</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,39 +1386,39 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95783582</v>
+        <v>118015387</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>58602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,23 +1428,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Göstorp,Nybro, Sm</t>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553374</v>
+        <v>553976</v>
       </c>
       <c r="R8" t="n">
-        <v>6286783</v>
+        <v>6287332</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,22 +1479,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En årsunge tiggde och blev matad av en adult hane</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,44 +1514,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118015387</v>
+        <v>115726461</v>
       </c>
       <c r="B9" t="n">
-        <v>58602</v>
+        <v>58676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1557,15 +1559,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1605,27 +1607,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En årsunge tiggde och blev matad av en adult hane</t>
+          <t>I dungen rakt väster om Madesjövägen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,134 +1651,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>115726461</v>
-      </c>
-      <c r="B10" t="n">
-        <v>58676</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Emberiza citrinella</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>553976</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6287332</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Nybro</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Madesjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I dungen rakt väster om Madesjövägen</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Ulf Edberg</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Ulf Edberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 2365-2025 artfynd.xlsx
+++ b/artfynd/S 2365-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1032,32 +1032,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77690699</v>
+        <v>134910787</v>
       </c>
       <c r="B5" t="n">
-        <v>58129</v>
+        <v>45050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102623</v>
+        <v>102018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,31 +1065,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+          <t>925 m OSO Petersborg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553976</v>
+        <v>553958</v>
       </c>
       <c r="R5" t="n">
-        <v>6287332</v>
+        <v>6286375</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,22 +1110,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På Hieracium canistrale-korg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,28 +1129,39 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt mot dike</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79153696</v>
+        <v>77690699</v>
       </c>
       <c r="B6" t="n">
-        <v>58039</v>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,37 +1169,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1236,27 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2019-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2019-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I hagen väster om vägen i ett slånsnår</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1281,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95783582</v>
+        <v>79153696</v>
       </c>
       <c r="B7" t="n">
-        <v>58327</v>
+        <v>58039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,42 +1292,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Göstorp,Nybro, Sm</t>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553374</v>
+        <v>553976</v>
       </c>
       <c r="R7" t="n">
-        <v>6286783</v>
+        <v>6287332</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1356,22 +1362,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I hagen väster om vägen i ett slånsnår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1386,39 +1397,39 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118015387</v>
+        <v>95783582</v>
       </c>
       <c r="B8" t="n">
-        <v>58602</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1428,31 +1439,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+          <t>Göstorp,Nybro, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553976</v>
+        <v>553374</v>
       </c>
       <c r="R8" t="n">
-        <v>6287332</v>
+        <v>6286783</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,27 +1482,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En årsunge tiggde och blev matad av en adult hane</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,44 +1512,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115726461</v>
+        <v>118015387</v>
       </c>
       <c r="B9" t="n">
-        <v>58676</v>
+        <v>58602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1559,15 +1557,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1607,27 +1605,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I dungen rakt väster om Madesjövägen</t>
+          <t>En årsunge tiggde och blev matad av en adult hane</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,6 +1649,134 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115726461</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>553976</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6287332</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I dungen rakt väster om Madesjövägen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulf Edberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulf Edberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 2365-2025 artfynd.xlsx
+++ b/artfynd/S 2365-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71407519</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77690698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,35 +1044,40 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/29379</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134910787</v>
+        <v>77690699</v>
       </c>
       <c r="B5" t="n">
-        <v>45050</v>
+        <v>58129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102018</v>
+        <v>102623</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1065,28 +1085,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>925 m OSO Petersborg, Sm</t>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553958</v>
+        <v>553976</v>
       </c>
       <c r="R5" t="n">
-        <v>6286375</v>
+        <v>6287332</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,17 +1133,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På Hieracium canistrale-korg</t>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,39 +1157,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Vägslänt mot dike</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Eric Lundén</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Nilsson</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Nilsson</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77690699</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>77690699</v>
+        <v>79153696</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>58039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1169,37 +1191,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102623</v>
+        <v>102626</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1239,22 +1261,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I hagen väster om vägen i ett slånsnår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,13 +1305,18 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79153696</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79153696</v>
+        <v>95783582</v>
       </c>
       <c r="B7" t="n">
-        <v>58039</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,50 +1324,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102626</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+          <t>Göstorp,Nybro, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553976</v>
+        <v>553374</v>
       </c>
       <c r="R7" t="n">
-        <v>6287332</v>
+        <v>6286783</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1362,27 +1386,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>I hagen väster om vägen i ett slånsnår</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,39 +1416,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783582</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95783582</v>
+        <v>118015387</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>58602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103042</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1439,23 +1463,31 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>föda åt ungar</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Göstorp,Nybro, Sm</t>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553374</v>
+        <v>553976</v>
       </c>
       <c r="R8" t="n">
-        <v>6286783</v>
+        <v>6287332</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1482,22 +1514,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En årsunge tiggde och blev matad av en adult hane</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,44 +1549,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118015387</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118015387</v>
+        <v>115726461</v>
       </c>
       <c r="B9" t="n">
-        <v>58602</v>
+        <v>58676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103042</v>
+        <v>103055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1557,15 +1599,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1605,27 +1647,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En årsunge tiggde och blev matad av en adult hane</t>
+          <t>I dungen rakt väster om Madesjövägen</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,136 +1691,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>115726461</v>
-      </c>
-      <c r="B10" t="n">
-        <v>58676</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Emberiza citrinella</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>553976</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6287332</v>
-      </c>
-      <c r="S10" t="n">
-        <v>25</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Nybro</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Madesjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I dungen rakt väster om Madesjövägen</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Ulf Edberg</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Ulf Edberg</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115726461</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 2365-2025 artfynd.xlsx
+++ b/artfynd/S 2365-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,32 +1052,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>77690699</v>
+        <v>134910787</v>
       </c>
       <c r="B5" t="n">
-        <v>58129</v>
+        <v>45055</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102623</v>
+        <v>102018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scheven, 1777)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,31 +1085,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+          <t>925 m OSO Petersborg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553976</v>
+        <v>553958</v>
       </c>
       <c r="R5" t="n">
-        <v>6287332</v>
+        <v>6286375</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1130,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På Hieracium canistrale-korg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,33 +1149,44 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägslänt mot dike</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Eric Lundén</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77690699</t>
+          <t>https://artportalen.se/Sighting/134910787</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79153696</v>
+        <v>77690699</v>
       </c>
       <c r="B6" t="n">
-        <v>58039</v>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,37 +1194,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102626</v>
+        <v>102623</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1261,27 +1264,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2019-05-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2019-07-29</t>
+          <t>2019-05-11</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>I hagen väster om vägen i ett slånsnår</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,16 +1305,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79153696</t>
+          <t>https://artportalen.se/Sighting/77690699</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95783582</v>
+        <v>79153696</v>
       </c>
       <c r="B7" t="n">
-        <v>58327</v>
+        <v>58039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,42 +1322,50 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>102626</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Göstorp,Nybro, Sm</t>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553374</v>
+        <v>553976</v>
       </c>
       <c r="R7" t="n">
-        <v>6286783</v>
+        <v>6287332</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1386,22 +1392,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>I hagen väster om vägen i ett slånsnår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,44 +1427,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Holst</t>
+          <t>Ulf Edberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95783582</t>
+          <t>https://artportalen.se/Sighting/79153696</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118015387</v>
+        <v>95783582</v>
       </c>
       <c r="B8" t="n">
-        <v>58602</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1463,31 +1474,23 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+          <t>Göstorp,Nybro, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553976</v>
+        <v>553374</v>
       </c>
       <c r="R8" t="n">
-        <v>6287332</v>
+        <v>6286783</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1514,27 +1517,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En årsunge tiggde och blev matad av en adult hane</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1549,49 +1547,49 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulf Edberg</t>
+          <t>Mikael Holst</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118015387</t>
+          <t>https://artportalen.se/Sighting/95783582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115726461</v>
+        <v>118015387</v>
       </c>
       <c r="B9" t="n">
-        <v>58676</v>
+        <v>58602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103042</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1599,15 +1597,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1647,27 +1645,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I dungen rakt väster om Madesjövägen</t>
+          <t>En årsunge tiggde och blev matad av en adult hane</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1692,6 +1690,139 @@
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118015387</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>115726461</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vsk Alsjöholmsvägen/Gamla Örsjövägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>553976</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6287332</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Madesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I dungen rakt väster om Madesjövägen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulf Edberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulf Edberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/115726461</t>
         </is>
@@ -1707,6 +1838,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
